--- a/Assessment3_Giretharan_M.xlsx
+++ b/Assessment3_Giretharan_M.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/Giretharan-M/IncuBrix-Broll-Engine</t>
+          <t>https://github.com/GiretharanM/IncuBrix-Broll-Engine</t>
         </is>
       </c>
     </row>
